--- a/output/roomself_excel/12751.xlsx
+++ b/output/roomself_excel/12751.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37045</v>
+        <v>69688</v>
       </c>
       <c r="D2" t="n">
-        <v>1576</v>
+        <v>2116</v>
       </c>
       <c r="E2" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11481</v>
+        <v>234186</v>
       </c>
       <c r="D3" t="n">
-        <v>872</v>
+        <v>4616</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60003</v>
+        <v>93130</v>
       </c>
       <c r="D4" t="n">
-        <v>2180</v>
+        <v>2452</v>
       </c>
       <c r="E4" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>457852</v>
+        <v>76728</v>
       </c>
       <c r="D5" t="n">
-        <v>8664</v>
+        <v>2216</v>
       </c>
       <c r="E5" t="n">
-        <v>865</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>672</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93130</v>
+        <v>91770</v>
       </c>
       <c r="D6" t="n">
-        <v>2452</v>
+        <v>2428</v>
       </c>
       <c r="E6" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>76728</v>
+        <v>105294</v>
       </c>
       <c r="D7" t="n">
-        <v>2216</v>
+        <v>2596</v>
       </c>
       <c r="E7" t="n">
-        <v>317</v>
+        <v>167</v>
       </c>
       <c r="F7" t="n">
-        <v>276</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33075</v>
+        <v>37045</v>
       </c>
       <c r="D8" t="n">
-        <v>1488</v>
+        <v>1576</v>
       </c>
       <c r="E8" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>184210</v>
+        <v>17481</v>
       </c>
       <c r="D9" t="n">
-        <v>3532</v>
+        <v>1144</v>
       </c>
       <c r="E9" t="n">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48444</v>
+        <v>30640</v>
       </c>
       <c r="D10" t="n">
-        <v>2456</v>
+        <v>1452</v>
       </c>
       <c r="E10" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17481</v>
+        <v>21108</v>
       </c>
       <c r="D11" t="n">
-        <v>1144</v>
+        <v>1200</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30640</v>
+        <v>74554</v>
       </c>
       <c r="D12" t="n">
-        <v>1452</v>
+        <v>3096</v>
       </c>
       <c r="E12" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>74554</v>
+        <v>354</v>
       </c>
       <c r="D13" t="n">
-        <v>3096</v>
+        <v>260</v>
       </c>
       <c r="E13" t="n">
-        <v>863</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>354</v>
+        <v>62391</v>
       </c>
       <c r="D14" t="n">
-        <v>260</v>
+        <v>2324</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>60003</v>
       </c>
       <c r="D15" t="n">
-        <v>156</v>
+        <v>2180</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>62391</v>
+        <v>27336</v>
       </c>
       <c r="D16" t="n">
-        <v>2324</v>
+        <v>1616</v>
       </c>
       <c r="E16" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -806,10 +806,10 @@
         <v>1140</v>
       </c>
       <c r="E17" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>91770</v>
+        <v>184210</v>
       </c>
       <c r="D18" t="n">
-        <v>2428</v>
+        <v>3532</v>
       </c>
       <c r="E18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,86 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105294</v>
+        <v>11481</v>
       </c>
       <c r="D19" t="n">
-        <v>2596</v>
+        <v>872</v>
       </c>
       <c r="E19" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>327</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>153978</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4692</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33075</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1488</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" t="n">
+        <v>156</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12751.xlsx
+++ b/output/roomself_excel/12751.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
         </is>
       </c>
     </row>
@@ -475,12 +480,9 @@
       <c r="D2" t="n">
         <v>2116</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +499,9 @@
       <c r="D3" t="n">
         <v>4616</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +518,9 @@
       <c r="D4" t="n">
         <v>2452</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,10 +537,15 @@
       <c r="D5" t="n">
         <v>2216</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>12</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -563,12 +564,9 @@
       <c r="D6" t="n">
         <v>2428</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,10 +583,15 @@
       <c r="D7" t="n">
         <v>2596</v>
       </c>
-      <c r="E7" t="n">
-        <v>167</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" t="n">
         <v>11</v>
       </c>
     </row>
@@ -607,12 +610,9 @@
       <c r="D8" t="n">
         <v>1576</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +629,9 @@
       <c r="D9" t="n">
         <v>1144</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +648,9 @@
       <c r="D10" t="n">
         <v>1452</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +667,9 @@
       <c r="D11" t="n">
         <v>1200</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +686,9 @@
       <c r="D12" t="n">
         <v>3096</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +705,9 @@
       <c r="D13" t="n">
         <v>260</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +724,9 @@
       <c r="D14" t="n">
         <v>2324</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +743,9 @@
       <c r="D15" t="n">
         <v>2180</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +762,9 @@
       <c r="D16" t="n">
         <v>1616</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +781,9 @@
       <c r="D17" t="n">
         <v>1140</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +800,9 @@
       <c r="D18" t="n">
         <v>3532</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +819,9 @@
       <c r="D19" t="n">
         <v>872</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +838,9 @@
       <c r="D20" t="n">
         <v>4692</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +857,9 @@
       <c r="D21" t="n">
         <v>1488</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +876,9 @@
       <c r="D22" t="n">
         <v>156</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/12751.xlsx
+++ b/output/roomself_excel/12751.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
